--- a/healthcare_forms/026_surgical_pathology_report_form_template--healthcare_forms.xlsx
+++ b/healthcare_forms/026_surgical_pathology_report_form_template--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>normal_tumor</t>
+          <t>normal tumor</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>benign_malignant</t>
+          <t>benign malignant</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>diagnosis_1</t>
+          <t>diagnosis 1</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>diagnosis_2</t>
+          <t>diagnosis 2</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>diagnosis_3</t>
+          <t>diagnosis 3</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>diagnosis_1_1</t>
+          <t>diagnosis 1 1</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>diagnosis_1_2</t>
+          <t>diagnosis 1 2</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>diagnosis_1_3</t>
+          <t>diagnosis 1 3</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>diagnosis_2_1</t>
+          <t>diagnosis 2 1</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>diagnosis_2_2</t>
+          <t>diagnosis 2 2</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>diagnosis_2_3</t>
+          <t>diagnosis 2 3</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>diagnosis_3_1</t>
+          <t>diagnosis 3 1</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>diagnosis_3_2</t>
+          <t>diagnosis 3 2</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>diagnosis_3_3</t>
+          <t>diagnosis 3 3</t>
         </is>
       </c>
     </row>
